--- a/cache/stand.xlsx
+++ b/cache/stand.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="142">
   <si>
     <t>VOKO HS 1</t>
   </si>
@@ -134,15 +134,15 @@
     <t>Bladel DS 3</t>
   </si>
   <si>
+    <t>Volley Zuid DS 8</t>
+  </si>
+  <si>
     <t>VVC Best DS 3</t>
   </si>
   <si>
     <t>Pegasus DS 2</t>
   </si>
   <si>
-    <t>Volley Zuid DS 8</t>
-  </si>
-  <si>
     <t>Hilver DS 2</t>
   </si>
   <si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>Bok MB 1</t>
+  </si>
+  <si>
+    <t>Handhaving</t>
   </si>
   <si>
     <t>VOKO MB 2</t>
@@ -1588,22 +1591,22 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="H36">
-        <v>168</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1666,7 +1669,7 @@
         <v>39</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39">
         <v>7</v>
@@ -1675,13 +1678,13 @@
         <v>6</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="H39">
-        <v>272</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1692,22 +1695,22 @@
         <v>40</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G40">
-        <v>167</v>
+        <v>287</v>
       </c>
       <c r="H40">
-        <v>175</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1718,22 +1721,22 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="H41">
-        <v>50</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1859,22 +1862,22 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48">
+        <v>18</v>
+      </c>
+      <c r="E48">
         <v>14</v>
       </c>
-      <c r="E48">
-        <v>11</v>
-      </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>302</v>
+        <v>400</v>
       </c>
       <c r="H48">
-        <v>226</v>
+        <v>301</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1963,22 +1966,22 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G52">
-        <v>279</v>
+        <v>354</v>
       </c>
       <c r="H52">
-        <v>277</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3032,22 +3035,22 @@
         <v>90</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D101">
+        <v>23</v>
+      </c>
+      <c r="E101">
         <v>18</v>
       </c>
-      <c r="E101">
-        <v>14</v>
-      </c>
       <c r="F101">
         <v>2</v>
       </c>
       <c r="G101">
-        <v>391</v>
+        <v>491</v>
       </c>
       <c r="H101">
-        <v>274</v>
+        <v>353</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3084,7 +3087,7 @@
         <v>92</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103">
         <v>7</v>
@@ -3093,13 +3096,13 @@
         <v>6</v>
       </c>
       <c r="F103">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G103">
-        <v>260</v>
+        <v>339</v>
       </c>
       <c r="H103">
-        <v>273</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3127,6 +3130,9 @@
       <c r="H104">
         <v>487</v>
       </c>
+      <c r="I104" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105">
@@ -3156,10 +3162,10 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3196,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -3222,7 +3228,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C110">
         <v>3</v>
@@ -3248,7 +3254,7 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C111">
         <v>3</v>
@@ -3274,7 +3280,7 @@
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C112">
         <v>3</v>
@@ -3300,7 +3306,7 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -3323,10 +3329,10 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3363,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C117">
         <v>5</v>
@@ -3389,7 +3395,7 @@
         <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C118">
         <v>4</v>
@@ -3415,7 +3421,7 @@
         <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C119">
         <v>5</v>
@@ -3441,7 +3447,7 @@
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C120">
         <v>4</v>
@@ -3467,7 +3473,7 @@
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -3490,10 +3496,10 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -3530,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C125">
         <v>6</v>
@@ -3556,7 +3562,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C126">
         <v>5</v>
@@ -3582,7 +3588,7 @@
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -3608,7 +3614,7 @@
         <v>4</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C128">
         <v>6</v>
@@ -3634,7 +3640,7 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C129">
         <v>5</v>
@@ -3660,7 +3666,7 @@
         <v>6</v>
       </c>
       <c r="B130" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C130">
         <v>5</v>
@@ -3683,10 +3689,10 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -3723,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C134">
         <v>3</v>
@@ -3749,7 +3755,7 @@
         <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C135">
         <v>3</v>
@@ -3775,7 +3781,7 @@
         <v>3</v>
       </c>
       <c r="B136" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C136">
         <v>3</v>
@@ -3801,7 +3807,7 @@
         <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C137">
         <v>3</v>
@@ -3827,7 +3833,7 @@
         <v>5</v>
       </c>
       <c r="B138" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C138">
         <v>3</v>
@@ -3853,7 +3859,7 @@
         <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C139">
         <v>3</v>
@@ -3876,10 +3882,10 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -3916,7 +3922,7 @@
         <v>1</v>
       </c>
       <c r="B143" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C143">
         <v>4</v>
@@ -3942,7 +3948,7 @@
         <v>2</v>
       </c>
       <c r="B144" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C144">
         <v>4</v>
@@ -3968,7 +3974,7 @@
         <v>3</v>
       </c>
       <c r="B145" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C145">
         <v>4</v>
@@ -3994,7 +4000,7 @@
         <v>4</v>
       </c>
       <c r="B146" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C146">
         <v>4</v>
@@ -4020,7 +4026,7 @@
         <v>5</v>
       </c>
       <c r="B147" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C147">
         <v>4</v>
@@ -4043,10 +4049,10 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -4083,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="B151" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C151">
         <v>4</v>
@@ -4109,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="B152" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C152">
         <v>4</v>
@@ -4135,7 +4141,7 @@
         <v>3</v>
       </c>
       <c r="B153" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C153">
         <v>4</v>
@@ -4161,7 +4167,7 @@
         <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C154">
         <v>4</v>
@@ -4187,7 +4193,7 @@
         <v>5</v>
       </c>
       <c r="B155" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C155">
         <v>4</v>
@@ -4210,10 +4216,10 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -4250,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="B159" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C159">
         <v>4</v>
@@ -4276,7 +4282,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C160">
         <v>4</v>
@@ -4302,7 +4308,7 @@
         <v>3</v>
       </c>
       <c r="B161" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C161">
         <v>4</v>
@@ -4328,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="B162" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C162">
         <v>4</v>
@@ -4354,7 +4360,7 @@
         <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C163">
         <v>4</v>
@@ -4377,10 +4383,10 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -4417,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="B167" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -4443,7 +4449,7 @@
         <v>2</v>
       </c>
       <c r="B168" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C168">
         <v>3</v>
@@ -4469,7 +4475,7 @@
         <v>3</v>
       </c>
       <c r="B169" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C169">
         <v>2</v>
@@ -4495,7 +4501,7 @@
         <v>4</v>
       </c>
       <c r="B170" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C170">
         <v>4</v>
@@ -4518,10 +4524,10 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -4558,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="B174" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C174">
         <v>3</v>
@@ -4584,7 +4590,7 @@
         <v>2</v>
       </c>
       <c r="B175" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C175">
         <v>3</v>
@@ -4610,7 +4616,7 @@
         <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C176">
         <v>3</v>
@@ -4636,7 +4642,7 @@
         <v>4</v>
       </c>
       <c r="B177" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C177">
         <v>3</v>
@@ -4662,7 +4668,7 @@
         <v>5</v>
       </c>
       <c r="B178" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C178">
         <v>3</v>
@@ -4688,7 +4694,7 @@
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C179">
         <v>3</v>

--- a/cache/stand.xlsx
+++ b/cache/stand.xlsx
@@ -83,6 +83,12 @@
     <t>Seniorencompetitie, Dames Derde divisie B</t>
   </si>
   <si>
+    <t>Gepidae DS 1</t>
+  </si>
+  <si>
+    <t>Volley Lek en IJssel DS 2</t>
+  </si>
+  <si>
     <t>Spirit DS 1</t>
   </si>
   <si>
@@ -92,21 +98,15 @@
     <t>Vocala DS 1</t>
   </si>
   <si>
-    <t>Gepidae DS 1</t>
-  </si>
-  <si>
     <t>Bedovo DS 1</t>
   </si>
   <si>
+    <t>Hands up DS 1</t>
+  </si>
+  <si>
     <t>ODI DS 1</t>
   </si>
   <si>
-    <t>Hands up DS 1</t>
-  </si>
-  <si>
-    <t>Volley Lek en IJssel DS 2</t>
-  </si>
-  <si>
     <t>SOMAS/Activia DS 5</t>
   </si>
   <si>
@@ -131,6 +131,9 @@
     <t>Atak'55 DS 6</t>
   </si>
   <si>
+    <t>Pegasus DS 2</t>
+  </si>
+  <si>
     <t>Bladel DS 3</t>
   </si>
   <si>
@@ -140,9 +143,6 @@
     <t>VVC Best DS 3</t>
   </si>
   <si>
-    <t>Pegasus DS 2</t>
-  </si>
-  <si>
     <t>Hilver DS 2</t>
   </si>
   <si>
@@ -161,12 +161,12 @@
     <t>De Moriaan Symmachia Roosendaal HS 2</t>
   </si>
   <si>
+    <t>VV Stevo HS 1</t>
+  </si>
+  <si>
     <t>Ardito HS 1</t>
   </si>
   <si>
-    <t>VV Stevo HS 1</t>
-  </si>
-  <si>
     <t>VV-VAT HS 1</t>
   </si>
   <si>
@@ -176,12 +176,12 @@
     <t>Atak'55 HS 4</t>
   </si>
   <si>
+    <t>AVC '87 HS 2</t>
+  </si>
+  <si>
     <t>Ardito HS 2</t>
   </si>
   <si>
-    <t>AVC '87 HS 2</t>
-  </si>
-  <si>
     <t>Westphal Kozijnen CSS HS 1</t>
   </si>
   <si>
@@ -197,12 +197,12 @@
     <t>De Burgst Breda HS 6</t>
   </si>
   <si>
+    <t>De Burgst Breda HS 5</t>
+  </si>
+  <si>
     <t>ROWI HS 2</t>
   </si>
   <si>
-    <t>De Burgst Breda HS 5</t>
-  </si>
-  <si>
     <t>Brug HS 1</t>
   </si>
   <si>
@@ -272,12 +272,12 @@
     <t>Smash'66 MA 1</t>
   </si>
   <si>
+    <t>Voltena MA 1</t>
+  </si>
+  <si>
     <t>Sliedrecht Sport MA 2</t>
   </si>
   <si>
-    <t>Voltena MA 1</t>
-  </si>
-  <si>
     <t>Flits MA 1</t>
   </si>
   <si>
@@ -290,16 +290,16 @@
     <t>De Burgst Breda MB 1</t>
   </si>
   <si>
+    <t>Bok MB 1</t>
+  </si>
+  <si>
+    <t>Handhaving</t>
+  </si>
+  <si>
     <t>Volley Tilburg MB 1</t>
   </si>
   <si>
     <t>De Moriaan Symmachia Roosendaal MB 1</t>
-  </si>
-  <si>
-    <t>Bok MB 1</t>
-  </si>
-  <si>
-    <t>Handhaving</t>
   </si>
   <si>
     <t>VOKO MB 2</t>
@@ -1153,25 +1153,25 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>291</v>
+        <v>406</v>
       </c>
       <c r="H16">
-        <v>264</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1179,25 +1179,25 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>8</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="H17">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1208,22 +1208,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
         <v>9</v>
       </c>
-      <c r="E18">
-        <v>8</v>
-      </c>
       <c r="F18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>303</v>
+        <v>371</v>
       </c>
       <c r="H18">
-        <v>295</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1234,22 +1234,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>199</v>
+        <v>308</v>
       </c>
       <c r="H19">
-        <v>179</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1263,19 +1263,19 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H20">
-        <v>317</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1286,7 +1286,7 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -1295,13 +1295,13 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="H21">
-        <v>294</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1312,22 +1312,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>6</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="H22">
-        <v>300</v>
+        <v>394</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1364,22 +1364,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G24">
-        <v>271</v>
+        <v>351</v>
       </c>
       <c r="H24">
-        <v>277</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1617,22 +1617,22 @@
         <v>37</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37">
-        <v>292</v>
+        <v>389</v>
       </c>
       <c r="H37">
-        <v>288</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1643,22 +1643,22 @@
         <v>38</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F38">
         <v>3</v>
       </c>
       <c r="G38">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="H38">
-        <v>159</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1681,10 +1681,10 @@
         <v>3</v>
       </c>
       <c r="G39">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="H39">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1695,7 +1695,7 @@
         <v>40</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>7</v>
@@ -1704,13 +1704,13 @@
         <v>6</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="H40">
-        <v>272</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1721,22 +1721,22 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G41">
-        <v>167</v>
+        <v>287</v>
       </c>
       <c r="H41">
-        <v>175</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1773,22 +1773,22 @@
         <v>43</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G43">
-        <v>140</v>
+        <v>211</v>
       </c>
       <c r="H43">
-        <v>168</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1799,7 +1799,7 @@
         <v>44</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1808,13 +1808,13 @@
         <v>2</v>
       </c>
       <c r="F44">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G44">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="H44">
-        <v>405</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1891,19 +1891,19 @@
         <v>4</v>
       </c>
       <c r="D49">
+        <v>18</v>
+      </c>
+      <c r="E49">
         <v>14</v>
       </c>
-      <c r="E49">
-        <v>11</v>
-      </c>
       <c r="F49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="H49">
-        <v>316</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -1914,22 +1914,22 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G50">
-        <v>291</v>
+        <v>366</v>
       </c>
       <c r="H50">
-        <v>232</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -1940,22 +1940,22 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G51">
-        <v>268</v>
+        <v>365</v>
       </c>
       <c r="H51">
-        <v>242</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2018,7 +2018,7 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D54">
         <v>5</v>
@@ -2027,13 +2027,13 @@
         <v>5</v>
       </c>
       <c r="F54">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G54">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="H54">
-        <v>303</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2053,13 +2053,13 @@
         <v>5</v>
       </c>
       <c r="F55">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G55">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="H55">
-        <v>389</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2096,22 +2096,22 @@
         <v>55</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G57">
-        <v>311</v>
+        <v>397</v>
       </c>
       <c r="H57">
-        <v>409</v>
+        <v>506</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2159,22 +2159,22 @@
         <v>58</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E61">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G61">
-        <v>393</v>
+        <v>477</v>
       </c>
       <c r="H61">
-        <v>304</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2211,22 +2211,22 @@
         <v>60</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D63">
+        <v>13</v>
+      </c>
+      <c r="E63">
+        <v>11</v>
+      </c>
+      <c r="F63">
         <v>10</v>
       </c>
-      <c r="E63">
-        <v>8</v>
-      </c>
-      <c r="F63">
-        <v>4</v>
-      </c>
       <c r="G63">
-        <v>284</v>
+        <v>479</v>
       </c>
       <c r="H63">
-        <v>248</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2237,22 +2237,22 @@
         <v>61</v>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E64">
         <v>8</v>
       </c>
       <c r="F64">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G64">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="H64">
-        <v>402</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2505,25 +2505,25 @@
         <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G76">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="H76">
-        <v>311</v>
+        <v>196</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2531,25 +2531,25 @@
         <v>6</v>
       </c>
       <c r="B77" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G77">
-        <v>62</v>
+        <v>209</v>
       </c>
       <c r="H77">
-        <v>100</v>
+        <v>311</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2560,22 +2560,22 @@
         <v>72</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G78">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="H78">
-        <v>200</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2868,22 +2868,22 @@
         <v>84</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D93">
+        <v>18</v>
+      </c>
+      <c r="E93">
         <v>15</v>
       </c>
-      <c r="E93">
-        <v>12</v>
-      </c>
       <c r="F93">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G93">
-        <v>394</v>
+        <v>505</v>
       </c>
       <c r="H93">
-        <v>313</v>
+        <v>408</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -2920,22 +2920,22 @@
         <v>85</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E95">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F95">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G95">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="H95">
-        <v>272</v>
+        <v>370</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -2946,22 +2946,22 @@
         <v>86</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E96">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F96">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G96">
-        <v>257</v>
+        <v>370</v>
       </c>
       <c r="H96">
-        <v>271</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -2972,22 +2972,22 @@
         <v>87</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G97">
-        <v>217</v>
+        <v>316</v>
       </c>
       <c r="H97">
-        <v>300</v>
+        <v>406</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3061,22 +3061,25 @@
         <v>91</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D102">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E102">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F102">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G102">
-        <v>357</v>
+        <v>518</v>
       </c>
       <c r="H102">
-        <v>361</v>
+        <v>561</v>
+      </c>
+      <c r="I102" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3084,25 +3087,25 @@
         <v>3</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C103">
         <v>4</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E103">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F103">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G103">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="H103">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3110,28 +3113,25 @@
         <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D104">
         <v>7</v>
       </c>
       <c r="E104">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F104">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G104">
-        <v>423</v>
+        <v>339</v>
       </c>
       <c r="H104">
-        <v>487</v>
-      </c>
-      <c r="I104" t="s">
-        <v>94</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3142,22 +3142,22 @@
         <v>88</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F105">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G105">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="H105">
-        <v>201</v>
+        <v>296</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3231,22 +3231,22 @@
         <v>98</v>
       </c>
       <c r="C110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D110">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E110">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110">
-        <v>296</v>
+        <v>396</v>
       </c>
       <c r="H110">
-        <v>150</v>
+        <v>203</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3254,10 +3254,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D111">
         <v>7</v>
@@ -3266,13 +3266,13 @@
         <v>6</v>
       </c>
       <c r="F111">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G111">
-        <v>232</v>
+        <v>331</v>
       </c>
       <c r="H111">
-        <v>261</v>
+        <v>326</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3280,25 +3280,25 @@
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F112">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G112">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="H112">
-        <v>285</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -3309,7 +3309,7 @@
         <v>100</v>
       </c>
       <c r="C113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -3318,13 +3318,13 @@
         <v>0</v>
       </c>
       <c r="F113">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G113">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="H113">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3421,25 +3421,25 @@
         <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C119">
         <v>5</v>
       </c>
       <c r="D119">
+        <v>11</v>
+      </c>
+      <c r="E119">
         <v>10</v>
       </c>
-      <c r="E119">
-        <v>9</v>
-      </c>
       <c r="F119">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G119">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="H119">
-        <v>492</v>
+        <v>440</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3447,25 +3447,25 @@
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D120">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E120">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F120">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G120">
-        <v>351</v>
+        <v>452</v>
       </c>
       <c r="H120">
-        <v>351</v>
+        <v>492</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3476,22 +3476,22 @@
         <v>106</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G121">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="H121">
-        <v>183</v>
+        <v>278</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -3539,22 +3539,22 @@
         <v>109</v>
       </c>
       <c r="C125">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D125">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E125">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
       <c r="G125">
-        <v>593</v>
+        <v>693</v>
       </c>
       <c r="H125">
-        <v>302</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -3565,22 +3565,22 @@
         <v>110</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D126">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E126">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G126">
-        <v>483</v>
+        <v>580</v>
       </c>
       <c r="H126">
-        <v>317</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -3591,7 +3591,7 @@
         <v>111</v>
       </c>
       <c r="C127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D127">
         <v>20</v>
@@ -3600,13 +3600,13 @@
         <v>16</v>
       </c>
       <c r="F127">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G127">
-        <v>443</v>
+        <v>516</v>
       </c>
       <c r="H127">
-        <v>341</v>
+        <v>441</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -3617,22 +3617,22 @@
         <v>112</v>
       </c>
       <c r="C128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F128">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G128">
-        <v>385</v>
+        <v>453</v>
       </c>
       <c r="H128">
-        <v>529</v>
+        <v>626</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -3640,25 +3640,25 @@
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C129">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F129">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G129">
-        <v>289</v>
+        <v>375</v>
       </c>
       <c r="H129">
-        <v>487</v>
+        <v>578</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -3666,25 +3666,25 @@
         <v>6</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G130">
-        <v>277</v>
+        <v>373</v>
       </c>
       <c r="H130">
-        <v>494</v>
+        <v>585</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4452,22 +4452,22 @@
         <v>137</v>
       </c>
       <c r="C168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D168">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E168">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F168">
         <v>3</v>
       </c>
       <c r="G168">
-        <v>278</v>
+        <v>378</v>
       </c>
       <c r="H168">
-        <v>210</v>
+        <v>291</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -4478,7 +4478,7 @@
         <v>140</v>
       </c>
       <c r="C169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D169">
         <v>4</v>
@@ -4487,13 +4487,13 @@
         <v>4</v>
       </c>
       <c r="F169">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G169">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="H169">
-        <v>173</v>
+        <v>273</v>
       </c>
     </row>
     <row r="170" spans="1:9">

--- a/cache/stand.xlsx
+++ b/cache/stand.xlsx
@@ -65,15 +65,15 @@
     <t>Atak'55 HS 2</t>
   </si>
   <si>
+    <t>Next Volley Dordrecht HS 4</t>
+  </si>
+  <si>
     <t>Volley Zuid HS 2</t>
   </si>
   <si>
     <t>Udenhout HS 1</t>
   </si>
   <si>
-    <t>Next Volley Dordrecht HS 4</t>
-  </si>
-  <si>
     <t>Donki Sjot HS 2</t>
   </si>
   <si>
@@ -86,6 +86,9 @@
     <t>Gepidae DS 1</t>
   </si>
   <si>
+    <t>Vocala DS 1</t>
+  </si>
+  <si>
     <t>Volley Lek en IJssel DS 2</t>
   </si>
   <si>
@@ -95,15 +98,12 @@
     <t>Minerva DS 1</t>
   </si>
   <si>
-    <t>Vocala DS 1</t>
+    <t>Hands up DS 1</t>
   </si>
   <si>
     <t>Bedovo DS 1</t>
   </si>
   <si>
-    <t>Hands up DS 1</t>
-  </si>
-  <si>
     <t>ODI DS 1</t>
   </si>
   <si>
@@ -137,12 +137,12 @@
     <t>Bladel DS 3</t>
   </si>
   <si>
+    <t>VVC Best DS 3</t>
+  </si>
+  <si>
     <t>Volley Zuid DS 8</t>
   </si>
   <si>
-    <t>VVC Best DS 3</t>
-  </si>
-  <si>
     <t>Hilver DS 2</t>
   </si>
   <si>
@@ -194,21 +194,21 @@
     <t>Westphal Kozijnen CSS HS 2</t>
   </si>
   <si>
+    <t>ROWI HS 2</t>
+  </si>
+  <si>
     <t>De Burgst Breda HS 6</t>
   </si>
   <si>
     <t>De Burgst Breda HS 5</t>
   </si>
   <si>
-    <t>ROWI HS 2</t>
+    <t>VV Stevo HS 2</t>
   </si>
   <si>
     <t>Brug HS 1</t>
   </si>
   <si>
-    <t>VV Stevo HS 2</t>
-  </si>
-  <si>
     <t>Condor HS 3</t>
   </si>
   <si>
@@ -221,21 +221,21 @@
     <t>Voltena HS 1</t>
   </si>
   <si>
+    <t>VC WIK Groot-Ammers HS 7</t>
+  </si>
+  <si>
     <t>WHV HS 3</t>
   </si>
   <si>
-    <t>VC WIK Groot-Ammers HS 7</t>
-  </si>
-  <si>
     <t>Molenwiek'74 HS 1</t>
   </si>
   <si>
+    <t>De Burgst Breda HS 7</t>
+  </si>
+  <si>
     <t>Spirit HS 6</t>
   </si>
   <si>
-    <t>De Burgst Breda HS 7</t>
-  </si>
-  <si>
     <t>VOKO HS 5</t>
   </si>
   <si>
@@ -245,19 +245,19 @@
     <t>Mytilus HS 2</t>
   </si>
   <si>
+    <t>Gepidae HS 3</t>
+  </si>
+  <si>
     <t>VV-VAT HS 2</t>
   </si>
   <si>
-    <t>Gepidae HS 3</t>
+    <t>Bok HS 1</t>
   </si>
   <si>
     <t>Gavoc'10 HS 3</t>
   </si>
   <si>
     <t>AVC '87 HS 3</t>
-  </si>
-  <si>
-    <t>Bok HS 1</t>
   </si>
   <si>
     <t>Ardito HS 3</t>
@@ -885,22 +885,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>298</v>
+        <v>390</v>
       </c>
       <c r="H4">
-        <v>244</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -911,22 +911,22 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>289</v>
+        <v>363</v>
       </c>
       <c r="H5">
-        <v>247</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -937,22 +937,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>316</v>
+        <v>417</v>
       </c>
       <c r="H6">
-        <v>291</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -963,22 +963,22 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>291</v>
+        <v>387</v>
       </c>
       <c r="H7">
-        <v>281</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -989,22 +989,22 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>341</v>
+        <v>275</v>
       </c>
       <c r="H8">
-        <v>406</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1018,19 +1018,19 @@
         <v>4</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="H9">
-        <v>418</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1041,22 +1041,22 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>181</v>
+        <v>360</v>
       </c>
       <c r="H10">
-        <v>192</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1064,25 +1064,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>177</v>
+        <v>326</v>
       </c>
       <c r="H11">
-        <v>202</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1090,10 +1090,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1102,13 +1102,13 @@
         <v>2</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="H12">
-        <v>314</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1153,25 +1153,25 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>4</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>11</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="H16">
-        <v>387</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1179,25 +1179,25 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>291</v>
+        <v>406</v>
       </c>
       <c r="H17">
-        <v>264</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1208,22 +1208,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18">
         <v>9</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>371</v>
+        <v>285</v>
       </c>
       <c r="H18">
-        <v>343</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1234,22 +1234,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19">
         <v>9</v>
       </c>
-      <c r="E19">
-        <v>8</v>
-      </c>
       <c r="F19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="H19">
-        <v>281</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1272,10 +1272,10 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="H20">
-        <v>295</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1286,22 +1286,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>199</v>
+        <v>303</v>
       </c>
       <c r="H21">
-        <v>179</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1318,16 +1318,16 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>11</v>
       </c>
       <c r="G22">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="H22">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1338,22 +1338,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>6</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>275</v>
+        <v>348</v>
       </c>
       <c r="H23">
-        <v>303</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1390,22 +1390,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="H25">
-        <v>196</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1669,22 +1669,22 @@
         <v>39</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="H39">
-        <v>159</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1695,22 +1695,22 @@
         <v>40</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
         <v>7</v>
       </c>
-      <c r="E40">
-        <v>6</v>
-      </c>
       <c r="F40">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G40">
-        <v>189</v>
+        <v>367</v>
       </c>
       <c r="H40">
-        <v>153</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1721,7 +1721,7 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41">
         <v>7</v>
@@ -1730,13 +1730,13 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="H41">
-        <v>272</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1992,22 +1992,22 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F53">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G53">
-        <v>271</v>
+        <v>376</v>
       </c>
       <c r="H53">
-        <v>280</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2018,22 +2018,22 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F54">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G54">
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="H54">
-        <v>389</v>
+        <v>494</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2188,19 +2188,19 @@
         <v>4</v>
       </c>
       <c r="D62">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G62">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H62">
-        <v>309</v>
+        <v>285</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2211,7 +2211,7 @@
         <v>60</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D63">
         <v>13</v>
@@ -2220,13 +2220,13 @@
         <v>11</v>
       </c>
       <c r="F63">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>479</v>
+        <v>389</v>
       </c>
       <c r="H63">
-        <v>486</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2237,22 +2237,22 @@
         <v>61</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64">
+        <v>13</v>
+      </c>
+      <c r="E64">
+        <v>11</v>
+      </c>
+      <c r="F64">
         <v>10</v>
       </c>
-      <c r="E64">
-        <v>8</v>
-      </c>
-      <c r="F64">
-        <v>4</v>
-      </c>
       <c r="G64">
-        <v>284</v>
+        <v>479</v>
       </c>
       <c r="H64">
-        <v>248</v>
+        <v>486</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2263,22 +2263,22 @@
         <v>62</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F65">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G65">
-        <v>328</v>
+        <v>460</v>
       </c>
       <c r="H65">
-        <v>390</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2289,22 +2289,22 @@
         <v>63</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G66">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="H66">
-        <v>397</v>
+        <v>490</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2315,22 +2315,22 @@
         <v>56</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G67">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="H67">
-        <v>77</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2430,22 +2430,22 @@
         <v>68</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E73">
         <v>8</v>
       </c>
       <c r="F73">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>279</v>
+        <v>200</v>
       </c>
       <c r="H73">
-        <v>223</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2456,22 +2456,22 @@
         <v>69</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c r="H74">
-        <v>74</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2546,10 +2546,10 @@
         <v>11</v>
       </c>
       <c r="G77">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H77">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2560,7 +2560,7 @@
         <v>72</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -2569,13 +2569,13 @@
         <v>2</v>
       </c>
       <c r="F78">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G78">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="H78">
-        <v>314</v>
+        <v>411</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2649,22 +2649,22 @@
         <v>76</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D83">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E83">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G83">
-        <v>297</v>
+        <v>467</v>
       </c>
       <c r="H83">
-        <v>186</v>
+        <v>430</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2675,22 +2675,22 @@
         <v>77</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E84">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F84">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G84">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="H84">
-        <v>361</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -2701,22 +2701,22 @@
         <v>78</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D85">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E85">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G85">
-        <v>197</v>
+        <v>277</v>
       </c>
       <c r="H85">
-        <v>159</v>
+        <v>259</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -2727,22 +2727,22 @@
         <v>79</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86">
+        <v>9</v>
+      </c>
+      <c r="E86">
         <v>7</v>
       </c>
-      <c r="E86">
-        <v>6</v>
-      </c>
       <c r="F86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G86">
-        <v>339</v>
+        <v>277</v>
       </c>
       <c r="H86">
-        <v>363</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2753,22 +2753,22 @@
         <v>80</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E87">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F87">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G87">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="H87">
-        <v>179</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:9">
